--- a/public/downloads/ComerUnraveling2022.xlsx
+++ b/public/downloads/ComerUnraveling2022.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>O</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
+  </si>
+  <si>
+    <t>O</t>
   </si>
 </sst>
 </file>
@@ -656,10 +679,10 @@
         <v>132</v>
       </c>
       <c r="N3" s="5">
-        <v>1539.475017309189</v>
+        <v>1539475.017309189</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03466739516988738</v>
+        <v>34.66739516988738</v>
       </c>
       <c r="P3" s="5">
         <v>44407</v>
@@ -706,10 +729,10 @@
         <v>132</v>
       </c>
       <c r="N4" s="5">
-        <v>878.1955261230469</v>
+        <v>878195.5261230469</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04427727771115493</v>
+        <v>44.27727771115493</v>
       </c>
       <c r="P4" s="5">
         <v>19834</v>
@@ -756,10 +779,10 @@
         <v>132</v>
       </c>
       <c r="N5" s="5">
-        <v>2845.995165109634</v>
+        <v>2845995.165109634</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1307301407951141</v>
+        <v>130.7301407951141</v>
       </c>
       <c r="P5" s="5">
         <v>21770</v>
@@ -806,10 +829,10 @@
         <v>132</v>
       </c>
       <c r="N6" s="5">
-        <v>2217.476626157761</v>
+        <v>2217476.626157761</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08814551123574992</v>
+        <v>88.14551123574992</v>
       </c>
       <c r="P6" s="5">
         <v>25157</v>
@@ -856,10 +879,10 @@
         <v>132</v>
       </c>
       <c r="N7" s="5">
-        <v>3515.142351150513</v>
+        <v>3515142.351150513</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1698546678497469</v>
+        <v>169.8546678497469</v>
       </c>
       <c r="P7" s="5">
         <v>20695</v>
@@ -906,10 +929,10 @@
         <v>132</v>
       </c>
       <c r="N8" s="5">
-        <v>327.9348356723785</v>
+        <v>327934.8356723785</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01243449117174301</v>
+        <v>12.43449117174301</v>
       </c>
       <c r="P8" s="5">
         <v>26373</v>
@@ -956,10 +979,10 @@
         <v>132</v>
       </c>
       <c r="N9" s="5">
-        <v>1086.81148314476</v>
+        <v>1086811.48314476</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03085866955747637</v>
+        <v>30.85866955747636</v>
       </c>
       <c r="P9" s="5">
         <v>35219</v>
@@ -1006,10 +1029,10 @@
         <v>132</v>
       </c>
       <c r="N10" s="5">
-        <v>2950.340090513229</v>
+        <v>2950340.090513229</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08374035225117023</v>
+        <v>83.74035225117022</v>
       </c>
       <c r="P10" s="5">
         <v>35232</v>
@@ -1056,10 +1079,10 @@
         <v>132</v>
       </c>
       <c r="N11" s="5">
-        <v>1273.740828752518</v>
+        <v>1273740.828752518</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04608991274976544</v>
+        <v>46.08991274976544</v>
       </c>
       <c r="P11" s="5">
         <v>27636</v>
@@ -1106,10 +1129,10 @@
         <v>132</v>
       </c>
       <c r="N12" s="5">
-        <v>368.9091427326202</v>
+        <v>368909.1427326202</v>
       </c>
       <c r="O12" s="4">
-        <v>0.0200091740919141</v>
+        <v>20.0091740919141</v>
       </c>
       <c r="P12" s="5">
         <v>18437</v>
@@ -1156,10 +1179,10 @@
         <v>132</v>
       </c>
       <c r="N13" s="5">
-        <v>2855.00584769249</v>
+        <v>2855005.84769249</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07770837908798284</v>
+        <v>77.70837908798283</v>
       </c>
       <c r="P13" s="5">
         <v>36740</v>
@@ -1206,10 +1229,10 @@
         <v>132</v>
       </c>
       <c r="N14" s="5">
-        <v>8969.011902332306</v>
+        <v>8969011.902332306</v>
       </c>
       <c r="O14" s="4">
-        <v>0.217715601085841</v>
+        <v>217.715601085841</v>
       </c>
       <c r="P14" s="5">
         <v>41196</v>
@@ -1256,10 +1279,10 @@
         <v>132</v>
       </c>
       <c r="N15" s="5">
-        <v>3591.326889753342</v>
+        <v>3591326.889753342</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2189566449063128</v>
+        <v>218.9566449063128</v>
       </c>
       <c r="P15" s="5">
         <v>16402</v>
@@ -1306,10 +1329,10 @@
         <v>132</v>
       </c>
       <c r="N16" s="5">
-        <v>7252.052951097488</v>
+        <v>7252052.951097488</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1001955394672141</v>
+        <v>100.1955394672141</v>
       </c>
       <c r="P16" s="5">
         <v>72379</v>
@@ -1356,10 +1379,10 @@
         <v>132</v>
       </c>
       <c r="N17" s="5">
-        <v>1448.101638555527</v>
+        <v>1448101.638555527</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09832970995827574</v>
+        <v>98.32970995827574</v>
       </c>
       <c r="P17" s="5">
         <v>14727</v>
@@ -1387,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1398,9 +1421,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1434,8 +1463,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1457,91 +1494,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4145993387618748</v>
+        <v>0.3627501333827945</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1552771548727728</v>
+        <v>0.1984265185563573</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1685493253749619</v>
+        <v>0.1723924519985041</v>
       </c>
       <c r="E3" s="4">
-        <v>86.55380333951787</v>
+        <v>80.61894454751588</v>
       </c>
       <c r="F3" s="4">
-        <v>87.76438885499378</v>
+        <v>82.15324384787438</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.02124332335242578</v>
+      </c>
+      <c r="O3" s="5">
+        <v>52</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3576002368125095</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1951583149636764</v>
+      </c>
+      <c r="R3" s="5">
+        <v>52</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4844871671330087</v>
+        <v>0.3449128512443165</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1375086340378797</v>
+        <v>0.2071926316076018</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1277640270044139</v>
+        <v>0.2055153752711023</v>
       </c>
       <c r="E4" s="4">
-        <v>84.02494331065809</v>
+        <v>84.15275200989423</v>
       </c>
       <c r="F4" s="4">
-        <v>85.99094976611873</v>
+        <v>86.83970578265959</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
       </c>
       <c r="H4" s="5">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>7</v>
+      </c>
+      <c r="K4" s="5">
         <v>3</v>
       </c>
-      <c r="J4" s="5">
-        <v>8</v>
-      </c>
-      <c r="K4" s="5">
-        <v>5</v>
-      </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.007825919205772464</v>
+      </c>
+      <c r="O4" s="5">
+        <v>59</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3457544906565772</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2082667692417539</v>
+      </c>
+      <c r="R4" s="5">
+        <v>59</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1552,6 +1643,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1559,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1570,9 +1662,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1606,8 +1704,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1629,91 +1735,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4585435188518743</v>
+        <v>0.4272434125772199</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1982261762032594</v>
+        <v>0.2712796254683806</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1807652155692928</v>
+        <v>0.2428441043969711</v>
       </c>
       <c r="E3" s="4">
-        <v>84.14914450628766</v>
+        <v>74.78148835291685</v>
       </c>
       <c r="F3" s="4">
-        <v>85.03948884821368</v>
+        <v>78.9973561114509</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" s="5">
         <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.02107897775181634</v>
+      </c>
+      <c r="O3" s="5">
+        <v>51</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4291993440481175</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2700910112980452</v>
+      </c>
+      <c r="R3" s="5">
+        <v>51</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3401068299422928</v>
+        <v>0.6275502797093627</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1620127137528394</v>
+        <v>0.3528348024936445</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1535529593293516</v>
+        <v>0.337770207383739</v>
       </c>
       <c r="E4" s="4">
-        <v>82.65357658214744</v>
+        <v>75.91991341991339</v>
       </c>
       <c r="F4" s="4">
-        <v>83.41603959053674</v>
+        <v>79.67476781235166</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
       </c>
       <c r="H4" s="5">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.2173562205424056</v>
+      </c>
+      <c r="O4" s="5">
+        <v>48</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6063167187986576</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3043179140540598</v>
+      </c>
+      <c r="R4" s="5">
+        <v>48</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1724,6 +1884,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1731,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1742,9 +1903,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1778,8 +1945,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1801,66 +1976,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3862859276720799</v>
+        <v>0.4844871671330087</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1901743843455431</v>
+        <v>0.1375086340378797</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1906346506594737</v>
+        <v>0.1277640270044139</v>
       </c>
       <c r="E3" s="4">
-        <v>89.65625644197023</v>
+        <v>84.02494331065809</v>
       </c>
       <c r="F3" s="4">
-        <v>91.10534878991311</v>
+        <v>85.99094976611873</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
+        <v>8</v>
+      </c>
+      <c r="K3" s="5">
+        <v>5</v>
+      </c>
+      <c r="L3" s="5">
         <v>3</v>
       </c>
-      <c r="K3" s="5">
-        <v>3</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.01195634885756279</v>
+      </c>
+      <c r="O3" s="5">
+        <v>55</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4844871671330087</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1359869169105535</v>
+      </c>
+      <c r="R3" s="5">
+        <v>55</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.291321009368932</v>
+        <v>0.4145993387618748</v>
       </c>
       <c r="C4" s="4">
-        <v>0.144047031040879</v>
+        <v>0.1552771548727728</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1388219359669429</v>
+        <v>0.1685493253749619</v>
       </c>
       <c r="E4" s="4">
-        <v>87.64945372088172</v>
+        <v>86.55380333951787</v>
       </c>
       <c r="F4" s="4">
-        <v>88.7414412582191</v>
+        <v>87.76438885499378</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
@@ -1869,23 +2080,41 @@
         <v>58</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.05850445056942401</v>
+      </c>
+      <c r="O4" s="5">
+        <v>58</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4155375836619397</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1502926283208375</v>
+      </c>
+      <c r="R4" s="5">
+        <v>58</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1896,6 +2125,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1903,7 +2133,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1914,9 +2144,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1950,8 +2186,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1973,66 +2217,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4062217899431072</v>
+        <v>0.3401068299422928</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1575688483012356</v>
+        <v>0.1620127137528394</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1604940545326193</v>
+        <v>0.1535529593293516</v>
       </c>
       <c r="E3" s="4">
-        <v>84.16615130900833</v>
+        <v>82.65357658214744</v>
       </c>
       <c r="F3" s="4">
-        <v>86.96207036811005</v>
+        <v>83.41603959053674</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.002800739846587419</v>
+      </c>
+      <c r="O3" s="5">
+        <v>55</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3395976045156405</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1618599461248437</v>
+      </c>
+      <c r="R3" s="5">
+        <v>55</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4359712605433211</v>
+        <v>0.4585435188518743</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2264326310914822</v>
+        <v>0.1982261762032594</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2273666037210706</v>
+        <v>0.1807652155692928</v>
       </c>
       <c r="E4" s="4">
-        <v>82.35157699443428</v>
+        <v>84.14914450628766</v>
       </c>
       <c r="F4" s="4">
-        <v>84.62358484170596</v>
+        <v>85.03948884821368</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
@@ -2041,23 +2321,41 @@
         <v>55</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
+        <v>10</v>
+      </c>
+      <c r="K4" s="5">
+        <v>3</v>
+      </c>
+      <c r="L4" s="5">
         <v>7</v>
       </c>
-      <c r="K4" s="5">
-        <v>6</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.06679043190940723</v>
+      </c>
+      <c r="O4" s="5">
+        <v>55</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4703126602349408</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2014198024595817</v>
+      </c>
+      <c r="R4" s="5">
+        <v>55</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2068,6 +2366,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2075,7 +2374,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2086,9 +2385,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2122,8 +2427,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2145,91 +2458,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.002252922734847</v>
+        <v>0.291321009368932</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5633784984990882</v>
+        <v>0.144047031040879</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6424359716258544</v>
+        <v>0.1388219359669429</v>
       </c>
       <c r="E3" s="4">
-        <v>68.58585858585838</v>
+        <v>87.64945372088172</v>
       </c>
       <c r="F3" s="4">
-        <v>74.4139380380997</v>
+        <v>88.7414412582191</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="I3" s="5">
+        <v>4</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
-        <v>17</v>
-      </c>
-      <c r="K3" s="5">
-        <v>8</v>
-      </c>
       <c r="L3" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.07007191630118163</v>
+      </c>
+      <c r="O3" s="5">
+        <v>58</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2622163815978738</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1181767907808315</v>
+      </c>
+      <c r="R3" s="5">
+        <v>58</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6670266087892475</v>
+        <v>0.3862859276720799</v>
       </c>
       <c r="C4" s="4">
-        <v>0.269527326859383</v>
+        <v>0.1901743843455431</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3092277278771883</v>
+        <v>0.1906346506594737</v>
       </c>
       <c r="E4" s="4">
-        <v>69.73768295196885</v>
+        <v>89.65625644197023</v>
       </c>
       <c r="F4" s="4">
-        <v>77.64287166971606</v>
+        <v>91.10534878991311</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
       </c>
       <c r="H4" s="5">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.03860904106452706</v>
+      </c>
+      <c r="O4" s="5">
+        <v>62</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3697092988382296</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.175019201462059</v>
+      </c>
+      <c r="R4" s="5">
+        <v>62</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2240,6 +2607,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2247,7 +2615,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2258,9 +2626,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2294,8 +2668,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2317,40 +2699,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4640177553075576</v>
+        <v>0.4359712605433211</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2750072112801875</v>
+        <v>0.2264326310914822</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2716688962950234</v>
+        <v>0.2273666037210706</v>
       </c>
       <c r="E3" s="4">
-        <v>89.68769325912183</v>
+        <v>82.35157699443428</v>
       </c>
       <c r="F3" s="4">
-        <v>90.54725103382935</v>
+        <v>84.62358484170596</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K3" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3" s="5">
         <v>1</v>
@@ -2358,25 +2758,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1943751549370077</v>
+      </c>
+      <c r="O3" s="5">
+        <v>55</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3390607694297748</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1241649952972282</v>
+      </c>
+      <c r="R3" s="5">
+        <v>55</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5438644279879185</v>
+        <v>0.4062217899431072</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3895953364798487</v>
+        <v>0.1575688483012356</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3825807916669801</v>
+        <v>0.1604940545326193</v>
       </c>
       <c r="E4" s="4">
-        <v>89.67584003298222</v>
+        <v>84.16615130900833</v>
       </c>
       <c r="F4" s="4">
-        <v>91.04247169683485</v>
+        <v>86.96207036811005</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
@@ -2385,13 +2803,13 @@
         <v>59</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
+        <v>7</v>
+      </c>
+      <c r="K4" s="5">
         <v>4</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
       </c>
       <c r="L4" s="5">
         <v>3</v>
@@ -2399,9 +2817,27 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.007403649582524647</v>
+      </c>
+      <c r="O4" s="5">
+        <v>59</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4081489282985624</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1590972022596665</v>
+      </c>
+      <c r="R4" s="5">
+        <v>59</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2412,6 +2848,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2419,7 +2856,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2430,9 +2867,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2466,8 +2909,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2489,91 +2940,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.406941053223717</v>
+        <v>0.6670266087892475</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7062821417280524</v>
+        <v>0.269527326859383</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7918629899333176</v>
+        <v>0.3092277278771883</v>
       </c>
       <c r="E3" s="4">
-        <v>58.41785198928063</v>
+        <v>69.73768295196885</v>
       </c>
       <c r="F3" s="4">
-        <v>64.94305470815574</v>
+        <v>77.64287166971606</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>15</v>
+      </c>
+      <c r="K3" s="5">
         <v>4</v>
       </c>
-      <c r="J3" s="5">
-        <v>29</v>
-      </c>
-      <c r="K3" s="5">
+      <c r="L3" s="5">
         <v>11</v>
       </c>
-      <c r="L3" s="5">
-        <v>18</v>
-      </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1687255319506957</v>
+      </c>
+      <c r="O3" s="5">
+        <v>49</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6017600223535065</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1712870962346686</v>
+      </c>
+      <c r="R3" s="5">
+        <v>49</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9339359224380872</v>
+        <v>1.002252922734847</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5109924634214508</v>
+        <v>0.5633784984990882</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5135748392502066</v>
+        <v>0.6424359716258544</v>
       </c>
       <c r="E4" s="4">
-        <v>61.89703153988877</v>
+        <v>68.58585858585838</v>
       </c>
       <c r="F4" s="4">
-        <v>69.78594671547653</v>
+        <v>74.4139380380997</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
       </c>
       <c r="H4" s="5">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I4" s="5">
         <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K4" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L4" s="5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.3687717428578802</v>
+      </c>
+      <c r="O4" s="5">
+        <v>46</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9931098920157776</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4380253587715026</v>
+      </c>
+      <c r="R4" s="5">
+        <v>46</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2584,6 +3089,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2591,7 +3097,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2602,9 +3108,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2638,8 +3150,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2661,91 +3181,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3780152115365511</v>
+        <v>0.5438644279879185</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2705666017781072</v>
+        <v>0.3895953364798487</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2585311026160772</v>
+        <v>0.3825807916669801</v>
       </c>
       <c r="E3" s="4">
-        <v>89.51041022469555</v>
+        <v>89.67584003298222</v>
       </c>
       <c r="F3" s="4">
-        <v>89.79916615822589</v>
+        <v>91.04247169683485</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
         <v>1</v>
       </c>
-      <c r="J3" s="5">
+      <c r="L3" s="5">
         <v>3</v>
       </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3809241676304118</v>
+      </c>
+      <c r="O3" s="5">
+        <v>59</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2411495265234379</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08389101066452909</v>
+      </c>
+      <c r="R3" s="5">
+        <v>59</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2870442521665701</v>
+        <v>0.4640177553075576</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2651905691663348</v>
+        <v>0.2750072112801875</v>
       </c>
       <c r="D4" s="4">
-        <v>0.257676336557904</v>
+        <v>0.2716688962950234</v>
       </c>
       <c r="E4" s="4">
-        <v>88.43692022263457</v>
+        <v>89.68769325912183</v>
       </c>
       <c r="F4" s="4">
-        <v>89.55189478679404</v>
+        <v>90.54725103382935</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
       </c>
       <c r="H4" s="5">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>5</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.2302978855912419</v>
+      </c>
+      <c r="O4" s="5">
+        <v>60</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3223200144524288</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1381594921027779</v>
+      </c>
+      <c r="R4" s="5">
+        <v>60</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2756,12 +3330,1352 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.9339359224380872</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5109924634214508</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.5135748392502066</v>
+      </c>
+      <c r="E3" s="4">
+        <v>61.89703153988877</v>
+      </c>
+      <c r="F3" s="4">
+        <v>69.78594671547653</v>
+      </c>
+      <c r="G3" s="5">
+        <v>66</v>
+      </c>
+      <c r="H3" s="5">
+        <v>43</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>20</v>
+      </c>
+      <c r="K3" s="5">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5">
+        <v>14</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.4929804585723163</v>
+      </c>
+      <c r="O3" s="5">
+        <v>43</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7530248439223374</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1545855758960396</v>
+      </c>
+      <c r="R3" s="5">
+        <v>43</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.406941053223717</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.7062821417280524</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.7918629899333176</v>
+      </c>
+      <c r="E4" s="4">
+        <v>58.41785198928063</v>
+      </c>
+      <c r="F4" s="4">
+        <v>64.94305470815574</v>
+      </c>
+      <c r="G4" s="5">
+        <v>66</v>
+      </c>
+      <c r="H4" s="5">
+        <v>33</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5">
+        <v>29</v>
+      </c>
+      <c r="K4" s="5">
+        <v>11</v>
+      </c>
+      <c r="L4" s="5">
+        <v>18</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.4748502474099966</v>
+      </c>
+      <c r="O4" s="5">
+        <v>33</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.416181157206347</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3998539785200312</v>
+      </c>
+      <c r="R4" s="5">
+        <v>31</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2870442521665701</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2651905691663348</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.257676336557904</v>
+      </c>
+      <c r="E3" s="4">
+        <v>88.43692022263457</v>
+      </c>
+      <c r="F3" s="4">
+        <v>89.55189478679404</v>
+      </c>
+      <c r="G3" s="5">
+        <v>66</v>
+      </c>
+      <c r="H3" s="5">
+        <v>58</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>5</v>
+      </c>
+      <c r="K3" s="5">
+        <v>2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2468265761497209</v>
+      </c>
+      <c r="O3" s="5">
+        <v>58</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1209790447674709</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09645858212502074</v>
+      </c>
+      <c r="R3" s="5">
+        <v>58</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3780152115365511</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2705666017781072</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2585311026160772</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.51041022469555</v>
+      </c>
+      <c r="F4" s="4">
+        <v>89.79916615822589</v>
+      </c>
+      <c r="G4" s="5">
+        <v>66</v>
+      </c>
+      <c r="H4" s="5">
+        <v>62</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2166541696864906</v>
+      </c>
+      <c r="O4" s="5">
+        <v>62</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.242755597886884</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1405582498082352</v>
+      </c>
+      <c r="R4" s="5">
+        <v>62</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>75</v>
+      </c>
+      <c r="C3" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="D3" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="E3" s="3">
+        <v>9.848484848484848</v>
+      </c>
+      <c r="F3" s="3">
+        <v>6.818181818181817</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4919295240089842</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1912737337382286</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1796131307095432</v>
+      </c>
+      <c r="K3" s="4">
+        <v>76.77205730777128</v>
+      </c>
+      <c r="L3" s="4">
+        <v>79.7421361263626</v>
+      </c>
+      <c r="M3" s="5">
+        <v>132</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1539475.017309189</v>
+      </c>
+      <c r="O3" s="4">
+        <v>34.66739516988738</v>
+      </c>
+      <c r="P3" s="5">
+        <v>44407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>82.57575757575758</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="D4" s="3">
+        <v>12.87878787878788</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="F4" s="3">
+        <v>9.848484848484848</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.3038364648992409</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.2337041063181899</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.2067103207104186</v>
+      </c>
+      <c r="K4" s="4">
+        <v>79.71835703978549</v>
+      </c>
+      <c r="L4" s="4">
+        <v>83.65153209951997</v>
+      </c>
+      <c r="M4" s="5">
+        <v>132</v>
+      </c>
+      <c r="N4" s="5">
+        <v>878195.5261230469</v>
+      </c>
+      <c r="O4" s="4">
+        <v>44.27727771115493</v>
+      </c>
+      <c r="P4" s="5">
+        <v>19834</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>87.87878787878788</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="D5" s="3">
+        <v>9.848484848484848</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="F5" s="3">
+        <v>5.303030303030303</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.344515116446364</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1639516097690043</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1675462629417466</v>
+      </c>
+      <c r="K5" s="4">
+        <v>84.25298907441727</v>
+      </c>
+      <c r="L5" s="4">
+        <v>87.24383092671793</v>
+      </c>
+      <c r="M5" s="5">
+        <v>132</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2845995.165109634</v>
+      </c>
+      <c r="O5" s="4">
+        <v>130.7301407951141</v>
+      </c>
+      <c r="P5" s="5">
+        <v>21770</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>84.09090909090909</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3.787878787878788</v>
+      </c>
+      <c r="D6" s="3">
+        <v>12.12121212121212</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.787878787878788</v>
+      </c>
+      <c r="F6" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.3581693304450327</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2012570439824828</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1951679596474923</v>
+      </c>
+      <c r="K6" s="4">
+        <v>82.80638012780898</v>
+      </c>
+      <c r="L6" s="4">
+        <v>85.61114500711905</v>
+      </c>
+      <c r="M6" s="5">
+        <v>132</v>
+      </c>
+      <c r="N6" s="5">
+        <v>2217476.626157761</v>
+      </c>
+      <c r="O6" s="4">
+        <v>88.14551123574992</v>
+      </c>
+      <c r="P6" s="5">
+        <v>25157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>86.36363636363636</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3.787878787878788</v>
+      </c>
+      <c r="D7" s="3">
+        <v>9.848484848484848</v>
+      </c>
+      <c r="E7" s="3">
+        <v>3.787878787878788</v>
+      </c>
+      <c r="F7" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.2470769747945377</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1072335361019085</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1059192629621992</v>
+      </c>
+      <c r="K7" s="4">
+        <v>87.32580911152297</v>
+      </c>
+      <c r="L7" s="4">
+        <v>89.39419361399166</v>
+      </c>
+      <c r="M7" s="5">
+        <v>132</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3515142.351150513</v>
+      </c>
+      <c r="O7" s="4">
+        <v>169.8546678497469</v>
+      </c>
+      <c r="P7" s="5">
+        <v>20695</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>84.09090909090909</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3.787878787878788</v>
+      </c>
+      <c r="D8" s="3">
+        <v>12.12121212121212</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="F8" s="3">
+        <v>9.848484848484848</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.3516773637345433</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.202125871742114</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1901962975521154</v>
+      </c>
+      <c r="K8" s="4">
+        <v>82.38584827870598</v>
+      </c>
+      <c r="L8" s="4">
+        <v>84.4964748152664</v>
+      </c>
+      <c r="M8" s="5">
+        <v>132</v>
+      </c>
+      <c r="N8" s="5">
+        <v>327934.8356723785</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12.43449117174301</v>
+      </c>
+      <c r="P8" s="5">
+        <v>26373</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>75</v>
+      </c>
+      <c r="C9" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="D9" s="3">
+        <v>18.93939393939394</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="F9" s="3">
+        <v>12.87878787878788</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.5177580314233875</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.2866858732403553</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.2613537700138544</v>
+      </c>
+      <c r="K9" s="4">
+        <v>75.35070088641534</v>
+      </c>
+      <c r="L9" s="4">
+        <v>79.33606196190013</v>
+      </c>
+      <c r="M9" s="5">
+        <v>132</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1086811.48314476</v>
+      </c>
+      <c r="O9" s="4">
+        <v>30.85866955747636</v>
+      </c>
+      <c r="P9" s="5">
+        <v>35219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>85.60606060606061</v>
+      </c>
+      <c r="C10" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9.848484848484848</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7.575757575757576</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2.272727272727273</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.4500123753974742</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1433296714397258</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1448631815301744</v>
+      </c>
+      <c r="K10" s="4">
+        <v>85.28937332508755</v>
+      </c>
+      <c r="L10" s="4">
+        <v>86.87766931055675</v>
+      </c>
+      <c r="M10" s="5">
+        <v>132</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2950340.090513229</v>
+      </c>
+      <c r="O10" s="4">
+        <v>83.74035225117022</v>
+      </c>
+      <c r="P10" s="5">
+        <v>35232</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D11" s="3">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="F11" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.4049551323752907</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1816398742922127</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1686967740216966</v>
+      </c>
+      <c r="K11" s="4">
+        <v>83.40136054421781</v>
+      </c>
+      <c r="L11" s="4">
+        <v>84.22776421937645</v>
+      </c>
+      <c r="M11" s="5">
+        <v>132</v>
+      </c>
+      <c r="N11" s="5">
+        <v>1273740.828752518</v>
+      </c>
+      <c r="O11" s="4">
+        <v>46.08991274976544</v>
+      </c>
+      <c r="P11" s="5">
+        <v>27636</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>90.90909090909091</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3.787878787878788</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5.303030303030303</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4.545454545454546</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.3159628402180517</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.147545369632799</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1445574559893458</v>
+      </c>
+      <c r="K12" s="4">
+        <v>88.65285508142607</v>
+      </c>
+      <c r="L12" s="4">
+        <v>89.92339502406521</v>
+      </c>
+      <c r="M12" s="5">
+        <v>132</v>
+      </c>
+      <c r="N12" s="5">
+        <v>368909.1427326202</v>
+      </c>
+      <c r="O12" s="4">
+        <v>20.0091740919141</v>
+      </c>
+      <c r="P12" s="5">
+        <v>18437</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>86.36363636363636</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D13" s="3">
+        <v>10.60606060606061</v>
+      </c>
+      <c r="E13" s="3">
+        <v>7.575757575757576</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.3736048488641686</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1422439445146305</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1415332351804637</v>
+      </c>
+      <c r="K13" s="4">
+        <v>83.2588641517213</v>
+      </c>
+      <c r="L13" s="4">
+        <v>85.79282760490806</v>
+      </c>
+      <c r="M13" s="5">
+        <v>132</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2855005.84769249</v>
+      </c>
+      <c r="O13" s="4">
+        <v>77.70837908798283</v>
+      </c>
+      <c r="P13" s="5">
+        <v>36740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>71.96969696969697</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3.787878787878788</v>
+      </c>
+      <c r="D14" s="3">
+        <v>24.24242424242424</v>
+      </c>
+      <c r="E14" s="3">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="F14" s="3">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.797434957184642</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.3004445707261883</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.3382397932373646</v>
+      </c>
+      <c r="K14" s="4">
+        <v>69.16177076891383</v>
+      </c>
+      <c r="L14" s="4">
+        <v>76.02840485390844</v>
+      </c>
+      <c r="M14" s="5">
+        <v>132</v>
+      </c>
+      <c r="N14" s="5">
+        <v>8969011.902332306</v>
+      </c>
+      <c r="O14" s="4">
+        <v>217.715601085841</v>
+      </c>
+      <c r="P14" s="5">
+        <v>41196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>90.15151515151516</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D15" s="3">
+        <v>6.818181818181817</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3.787878787878788</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.2817347704879333</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.111253270213226</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1162190895256763</v>
+      </c>
+      <c r="K15" s="4">
+        <v>89.68176664605306</v>
+      </c>
+      <c r="L15" s="4">
+        <v>90.79486136533048</v>
+      </c>
+      <c r="M15" s="5">
+        <v>132</v>
+      </c>
+      <c r="N15" s="5">
+        <v>3591326.889753342</v>
+      </c>
+      <c r="O15" s="4">
+        <v>218.9566449063128</v>
+      </c>
+      <c r="P15" s="5">
+        <v>16402</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>56.06060606060606</v>
+      </c>
+      <c r="C16" s="3">
+        <v>5.303030303030303</v>
+      </c>
+      <c r="D16" s="3">
+        <v>38.63636363636363</v>
+      </c>
+      <c r="E16" s="3">
+        <v>12.87878787878788</v>
+      </c>
+      <c r="F16" s="3">
+        <v>24.24242424242424</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1.515151515151515</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1.084603000564342</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2573331499682523</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.3806028066734234</v>
+      </c>
+      <c r="K16" s="4">
+        <v>60.15744176458471</v>
+      </c>
+      <c r="L16" s="4">
+        <v>67.36450071181682</v>
+      </c>
+      <c r="M16" s="5">
+        <v>132</v>
+      </c>
+      <c r="N16" s="5">
+        <v>7252052.951097488</v>
+      </c>
+      <c r="O16" s="4">
+        <v>100.1955394672141</v>
+      </c>
+      <c r="P16" s="5">
+        <v>72379</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>90.90909090909091</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D17" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1818673213271775</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1192434104280149</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.1197832618543381</v>
+      </c>
+      <c r="K17" s="4">
+        <v>88.97366522366443</v>
+      </c>
+      <c r="L17" s="4">
+        <v>89.67553047250941</v>
+      </c>
+      <c r="M17" s="5">
+        <v>132</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1448101.638555527</v>
+      </c>
+      <c r="O17" s="4">
+        <v>98.32970995827574</v>
+      </c>
+      <c r="P17" s="5">
+        <v>14727</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2875,16 +4789,16 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
         <v>3</v>
       </c>
-      <c r="L3" s="5">
-        <v>19</v>
-      </c>
-      <c r="M3" s="5">
-        <v>4</v>
-      </c>
       <c r="N3" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -2922,13 +4836,13 @@
         <v>0</v>
       </c>
       <c r="L4" s="5">
+        <v>7</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
         <v>11</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -2966,13 +4880,13 @@
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -3007,10 +4921,10 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
         <v>4</v>
-      </c>
-      <c r="L6" s="5">
-        <v>8</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
@@ -3054,13 +4968,13 @@
         <v>1</v>
       </c>
       <c r="L7" s="5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
       </c>
       <c r="N7" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" customHeight="1">
@@ -3095,16 +5009,16 @@
         <v>1</v>
       </c>
       <c r="K8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
       <c r="N8" s="5">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -3139,16 +5053,16 @@
         <v>2</v>
       </c>
       <c r="K9" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3183,16 +5097,16 @@
         <v>4</v>
       </c>
       <c r="K10" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M10" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -3227,16 +5141,16 @@
         <v>2</v>
       </c>
       <c r="K11" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -3271,16 +5185,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
         <v>1</v>
-      </c>
-      <c r="L12" s="5">
-        <v>6</v>
-      </c>
-      <c r="M12" s="5">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5">
-        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3315,16 +5229,16 @@
         <v>3</v>
       </c>
       <c r="K13" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L13" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
         <v>2</v>
-      </c>
-      <c r="N13" s="5">
-        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -3359,16 +5273,16 @@
         <v>2</v>
       </c>
       <c r="K14" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="5">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="M14" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3406,13 +5320,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
       </c>
       <c r="N15" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="25" customHeight="1">
@@ -3447,16 +5361,16 @@
         <v>6</v>
       </c>
       <c r="K16" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L16" s="5">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="M16" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N16" s="5">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3491,16 +5405,16 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
       </c>
       <c r="N17" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3516,9 +5430,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>99</v>
+      </c>
+      <c r="C3" s="5">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5">
+        <v>22</v>
+      </c>
+      <c r="E3" s="5">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5">
+        <v>9</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>13</v>
+      </c>
+      <c r="I3" s="5">
+        <v>13</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>6</v>
+      </c>
+      <c r="M3" s="5">
+        <v>3</v>
+      </c>
+      <c r="N3" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>109</v>
+      </c>
+      <c r="C4" s="5">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5">
+        <v>17</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5">
+        <v>13</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>7</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>116</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5">
+        <v>7</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>7</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>111</v>
+      </c>
+      <c r="C6" s="5">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5">
+        <v>5</v>
+      </c>
+      <c r="F6" s="5">
+        <v>11</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>5</v>
+      </c>
+      <c r="I6" s="5">
+        <v>5</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>4</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>114</v>
+      </c>
+      <c r="C7" s="5">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5">
+        <v>13</v>
+      </c>
+      <c r="E7" s="5">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5">
+        <v>8</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>5</v>
+      </c>
+      <c r="I7" s="5">
+        <v>5</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>7</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>111</v>
+      </c>
+      <c r="C8" s="5">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5">
+        <v>16</v>
+      </c>
+      <c r="E8" s="5">
+        <v>3</v>
+      </c>
+      <c r="F8" s="5">
+        <v>13</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5">
+        <v>3</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5">
+        <v>8</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>99</v>
+      </c>
+      <c r="C9" s="5">
+        <v>8</v>
+      </c>
+      <c r="D9" s="5">
+        <v>25</v>
+      </c>
+      <c r="E9" s="5">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5">
+        <v>17</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>8</v>
+      </c>
+      <c r="I9" s="5">
+        <v>8</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>7</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>113</v>
+      </c>
+      <c r="C10" s="5">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5">
+        <v>13</v>
+      </c>
+      <c r="E10" s="5">
+        <v>10</v>
+      </c>
+      <c r="F10" s="5">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>10</v>
+      </c>
+      <c r="I10" s="5">
+        <v>9</v>
+      </c>
+      <c r="J10" s="5">
+        <v>4</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>110</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5">
+        <v>18</v>
+      </c>
+      <c r="E11" s="5">
+        <v>6</v>
+      </c>
+      <c r="F11" s="5">
+        <v>12</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>6</v>
+      </c>
+      <c r="I11" s="5">
+        <v>6</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>6</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>120</v>
+      </c>
+      <c r="C12" s="5">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5">
+        <v>7</v>
+      </c>
+      <c r="E12" s="5">
+        <v>6</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>6</v>
+      </c>
+      <c r="I12" s="5">
+        <v>6</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>114</v>
+      </c>
+      <c r="C13" s="5">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5">
+        <v>14</v>
+      </c>
+      <c r="E13" s="5">
+        <v>10</v>
+      </c>
+      <c r="F13" s="5">
+        <v>4</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>10</v>
+      </c>
+      <c r="I13" s="5">
+        <v>9</v>
+      </c>
+      <c r="J13" s="5">
+        <v>3</v>
+      </c>
+      <c r="K13" s="5">
+        <v>1</v>
+      </c>
+      <c r="L13" s="5">
+        <v>3</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>95</v>
+      </c>
+      <c r="C14" s="5">
+        <v>5</v>
+      </c>
+      <c r="D14" s="5">
+        <v>32</v>
+      </c>
+      <c r="E14" s="5">
+        <v>12</v>
+      </c>
+      <c r="F14" s="5">
+        <v>20</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>12</v>
+      </c>
+      <c r="I14" s="5">
+        <v>11</v>
+      </c>
+      <c r="J14" s="5">
+        <v>2</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>15</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>119</v>
+      </c>
+      <c r="C15" s="5">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5">
+        <v>9</v>
+      </c>
+      <c r="E15" s="5">
+        <v>5</v>
+      </c>
+      <c r="F15" s="5">
+        <v>4</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>5</v>
+      </c>
+      <c r="I15" s="5">
+        <v>5</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>3</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>74</v>
+      </c>
+      <c r="C16" s="5">
+        <v>7</v>
+      </c>
+      <c r="D16" s="5">
+        <v>51</v>
+      </c>
+      <c r="E16" s="5">
+        <v>17</v>
+      </c>
+      <c r="F16" s="5">
+        <v>32</v>
+      </c>
+      <c r="G16" s="5">
+        <v>2</v>
+      </c>
+      <c r="H16" s="5">
+        <v>16</v>
+      </c>
+      <c r="I16" s="5">
+        <v>16</v>
+      </c>
+      <c r="J16" s="5">
+        <v>6</v>
+      </c>
+      <c r="K16" s="5">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5">
+        <v>21</v>
+      </c>
+      <c r="M16" s="5">
+        <v>1</v>
+      </c>
+      <c r="N16" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>120</v>
+      </c>
+      <c r="C17" s="5">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5">
+        <v>8</v>
+      </c>
+      <c r="E17" s="5">
+        <v>4</v>
+      </c>
+      <c r="F17" s="5">
+        <v>4</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>4</v>
+      </c>
+      <c r="I17" s="5">
+        <v>4</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3529,9 +6198,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3565,8 +6240,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3588,91 +6271,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4728076201950721</v>
+        <v>0.4969862021435993</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2261864868887897</v>
+        <v>0.1713455387627338</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2225953748539223</v>
+        <v>0.1673090945417903</v>
       </c>
       <c r="E3" s="4">
-        <v>78.51937744794859</v>
+        <v>75.02473716759444</v>
       </c>
       <c r="F3" s="4">
-        <v>81.74191580232008</v>
+        <v>77.74235645041006</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J3" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K3" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.03138994436115752</v>
+      </c>
+      <c r="O3" s="5">
+        <v>45</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5025936302794297</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1709127754609125</v>
+      </c>
+      <c r="R3" s="5">
+        <v>45</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4969862021435993</v>
+        <v>0.4728076201950721</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1713455387627338</v>
+        <v>0.2261864868887897</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1673090945417903</v>
+        <v>0.2225953748539223</v>
       </c>
       <c r="E4" s="4">
-        <v>75.02473716759444</v>
+        <v>78.51937744794859</v>
       </c>
       <c r="F4" s="4">
-        <v>77.74235645041006</v>
+        <v>81.74191580232008</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
       </c>
       <c r="H4" s="5">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I4" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K4" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.1472792623903235</v>
+      </c>
+      <c r="O4" s="5">
+        <v>54</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4812654177385385</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2082411989693254</v>
+      </c>
+      <c r="R4" s="5">
+        <v>54</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3683,14 +6420,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3701,9 +6439,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3737,8 +6481,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3760,91 +6512,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2750225447823449</v>
+        <v>0.3500191030894788</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2362035785357775</v>
+        <v>0.2538272987778405</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2274456613387783</v>
+        <v>0.2092006451219583</v>
       </c>
       <c r="E3" s="4">
-        <v>81.24201195629814</v>
+        <v>78.19470212327326</v>
       </c>
       <c r="F3" s="4">
-        <v>85.47742525930555</v>
+        <v>81.82563893973426</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="5">
         <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.01431298042295354</v>
+      </c>
+      <c r="O3" s="5">
+        <v>52</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3517540098074124</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2532767995308038</v>
+      </c>
+      <c r="R3" s="5">
+        <v>52</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3500191030894788</v>
+        <v>0.2750225447823449</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2538272987778405</v>
+        <v>0.2362035785357775</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2092006451219583</v>
+        <v>0.2274456613387783</v>
       </c>
       <c r="E4" s="4">
-        <v>78.19470212327326</v>
+        <v>81.24201195629814</v>
       </c>
       <c r="F4" s="4">
-        <v>81.82563893973426</v>
+        <v>85.47742525930555</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
       </c>
       <c r="H4" s="5">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I4" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" s="5">
         <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.1623651931226708</v>
+      </c>
+      <c r="O4" s="5">
+        <v>57</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2559189199910694</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2158483160189631</v>
+      </c>
+      <c r="R4" s="5">
+        <v>57</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3855,14 +6661,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3873,9 +6680,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3909,8 +6722,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3932,91 +6753,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4957077382674938</v>
+        <v>0.214953124397879</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1967788887276308</v>
+        <v>0.1499891467380368</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2013288010988937</v>
+        <v>0.1457733450065581</v>
       </c>
       <c r="E3" s="4">
-        <v>84.94227994228009</v>
+        <v>83.56369820655571</v>
       </c>
       <c r="F3" s="4">
-        <v>87.66880211511085</v>
+        <v>86.81885973832266</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.06706215144961752</v>
+      </c>
+      <c r="O3" s="5">
+        <v>57</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2002758117418247</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1365239505810064</v>
+      </c>
+      <c r="R3" s="5">
+        <v>57</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.214953124397879</v>
+        <v>0.4957077382674938</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1499891467380368</v>
+        <v>0.1967788887276308</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1457733450065581</v>
+        <v>0.2013288010988937</v>
       </c>
       <c r="E4" s="4">
-        <v>83.56369820655571</v>
+        <v>84.94227994228009</v>
       </c>
       <c r="F4" s="4">
-        <v>86.81885973832266</v>
+        <v>87.66880211511085</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
       </c>
       <c r="H4" s="5">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5">
         <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>-0.01709720897037778</v>
+      </c>
+      <c r="O4" s="5">
+        <v>59</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4887544211509035</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1904495177980869</v>
+      </c>
+      <c r="R4" s="5">
+        <v>59</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4027,14 +6902,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4045,9 +6921,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4081,8 +6963,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4104,91 +6994,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2293752166996615</v>
+        <v>0.4930445158893548</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2146681050812388</v>
+        <v>0.1902219648231002</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2182223431236668</v>
+        <v>0.1758083889618826</v>
       </c>
       <c r="E3" s="4">
-        <v>84.06977942692261</v>
+        <v>81.54298082869555</v>
       </c>
       <c r="F3" s="4">
-        <v>87.17815741305576</v>
+        <v>84.0441326011797</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.02391658558893968</v>
+      </c>
+      <c r="O3" s="5">
+        <v>53</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4836228306573483</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1834531198450985</v>
+      </c>
+      <c r="R3" s="5">
+        <v>53</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4930445158893548</v>
+        <v>0.2293752166996615</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1902219648231002</v>
+        <v>0.2146681050812388</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1758083889618826</v>
+        <v>0.2182223431236668</v>
       </c>
       <c r="E4" s="4">
-        <v>81.54298082869555</v>
+        <v>84.06977942692261</v>
       </c>
       <c r="F4" s="4">
-        <v>84.0441326011797</v>
+        <v>87.17815741305576</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
       </c>
       <c r="H4" s="5">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K4" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.01367851440703795</v>
+      </c>
+      <c r="O4" s="5">
+        <v>58</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2327158302327172</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2175261470735408</v>
+      </c>
+      <c r="R4" s="5">
+        <v>58</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4199,14 +7143,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4217,9 +7162,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4253,8 +7204,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4276,91 +7235,145 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3716146117755652</v>
+        <v>0.1141972774978897</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1300703023663086</v>
+        <v>0.07693105759176776</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1296791302311163</v>
+        <v>0.07966069728030732</v>
       </c>
       <c r="E3" s="4">
-        <v>87.72727272727302</v>
+        <v>86.92434549577342</v>
       </c>
       <c r="F3" s="4">
-        <v>89.43122500169564</v>
+        <v>89.35716222629081</v>
       </c>
       <c r="G3" s="5">
         <v>66</v>
       </c>
       <c r="H3" s="5">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
+        <v>7</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
         <v>6</v>
       </c>
-      <c r="K3" s="5">
-        <v>4</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.01485967995674807</v>
+      </c>
+      <c r="O3" s="5">
+        <v>56</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1097374242338208</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0727362076703115</v>
+      </c>
+      <c r="R3" s="5">
+        <v>56</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1141972774978897</v>
+        <v>0.3716146117755652</v>
       </c>
       <c r="C4" s="4">
-        <v>0.07693105759176776</v>
+        <v>0.1300703023663086</v>
       </c>
       <c r="D4" s="4">
-        <v>0.07966069728030732</v>
+        <v>0.1296791302311163</v>
       </c>
       <c r="E4" s="4">
-        <v>86.92434549577342</v>
+        <v>87.72727272727302</v>
       </c>
       <c r="F4" s="4">
-        <v>89.35716222629081</v>
+        <v>89.43122500169564</v>
       </c>
       <c r="G4" s="5">
         <v>66</v>
       </c>
       <c r="H4" s="5">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
+      <c r="N4" s="4">
+        <v>0.02970104342816024</v>
+      </c>
+      <c r="O4" s="5">
+        <v>58</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3844165253552547</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.14054130148414</v>
+      </c>
+      <c r="R4" s="5">
+        <v>58</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4371,350 +7384,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3449128512443165</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2071926316076018</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2055153752711023</v>
-      </c>
-      <c r="E3" s="4">
-        <v>84.15275200989423</v>
-      </c>
-      <c r="F3" s="4">
-        <v>86.83970578265959</v>
-      </c>
-      <c r="G3" s="5">
-        <v>66</v>
-      </c>
-      <c r="H3" s="5">
-        <v>59</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>7</v>
-      </c>
-      <c r="K3" s="5">
-        <v>3</v>
-      </c>
-      <c r="L3" s="5">
-        <v>4</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3627501333827945</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1984265185563573</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1723924519985041</v>
-      </c>
-      <c r="E4" s="4">
-        <v>80.61894454751588</v>
-      </c>
-      <c r="F4" s="4">
-        <v>82.15324384787438</v>
-      </c>
-      <c r="G4" s="5">
-        <v>66</v>
-      </c>
-      <c r="H4" s="5">
-        <v>52</v>
-      </c>
-      <c r="I4" s="5">
-        <v>5</v>
-      </c>
-      <c r="J4" s="5">
-        <v>9</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>9</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.6275502797093627</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3528348024936445</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.337770207383739</v>
-      </c>
-      <c r="E3" s="4">
-        <v>75.91991341991339</v>
-      </c>
-      <c r="F3" s="4">
-        <v>79.67476781235166</v>
-      </c>
-      <c r="G3" s="5">
-        <v>66</v>
-      </c>
-      <c r="H3" s="5">
-        <v>48</v>
-      </c>
-      <c r="I3" s="5">
-        <v>4</v>
-      </c>
-      <c r="J3" s="5">
-        <v>14</v>
-      </c>
-      <c r="K3" s="5">
-        <v>5</v>
-      </c>
-      <c r="L3" s="5">
-        <v>9</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4272434125772199</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2712796254683806</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2428441043969711</v>
-      </c>
-      <c r="E4" s="4">
-        <v>74.78148835291685</v>
-      </c>
-      <c r="F4" s="4">
-        <v>78.9973561114509</v>
-      </c>
-      <c r="G4" s="5">
-        <v>66</v>
-      </c>
-      <c r="H4" s="5">
-        <v>51</v>
-      </c>
-      <c r="I4" s="5">
-        <v>4</v>
-      </c>
-      <c r="J4" s="5">
-        <v>11</v>
-      </c>
-      <c r="K4" s="5">
-        <v>3</v>
-      </c>
-      <c r="L4" s="5">
-        <v>8</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/ComerUnraveling2022.xlsx
+++ b/public/downloads/ComerUnraveling2022.xlsx
@@ -1554,16 +1554,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02124332335242578</v>
+        <v>-0.04128592430811695</v>
       </c>
       <c r="O3" s="5">
         <v>52</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3576002368125095</v>
+        <v>0.3537920912100952</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1951583149636764</v>
+        <v>0.1934083764614878</v>
       </c>
       <c r="R3" s="5">
         <v>52</v>
@@ -1613,16 +1613,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.007825919205772464</v>
+        <v>-0.01559937368215802</v>
       </c>
       <c r="O4" s="5">
         <v>59</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3457544906565772</v>
+        <v>0.3438574306600395</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2082667692417539</v>
+        <v>0.2057475954678654</v>
       </c>
       <c r="R4" s="5">
         <v>59</v>
@@ -1795,16 +1795,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.02107897775181634</v>
+        <v>0.03334070949892975</v>
       </c>
       <c r="O3" s="5">
         <v>51</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4291993440481175</v>
+        <v>0.4306856145629191</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2700910112980452</v>
+        <v>0.2698505851853567</v>
       </c>
       <c r="R3" s="5">
         <v>51</v>
@@ -1854,16 +1854,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2173562205424056</v>
+        <v>0.1867152616516279</v>
       </c>
       <c r="O4" s="5">
         <v>48</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6063167187986576</v>
+        <v>0.6009519251241447</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3043179140540598</v>
+        <v>0.3020481492334011</v>
       </c>
       <c r="R4" s="5">
         <v>48</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01195634885756279</v>
+        <v>0.05939002282618944</v>
       </c>
       <c r="O3" s="5">
         <v>55</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4844871671330087</v>
+        <v>0.4863624629287167</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1359869169105535</v>
+        <v>0.1322002588148506</v>
       </c>
       <c r="R3" s="5">
         <v>55</v>
@@ -2095,16 +2095,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.05850445056942401</v>
+        <v>0.04358980025885151</v>
       </c>
       <c r="O4" s="5">
         <v>58</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4155375836619397</v>
+        <v>0.4137275100311654</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1502926283208375</v>
+        <v>0.1497757842213947</v>
       </c>
       <c r="R4" s="5">
         <v>58</v>
@@ -2277,16 +2277,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.002800739846587419</v>
+        <v>-0.02020950535154498</v>
       </c>
       <c r="O3" s="5">
         <v>55</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3395976045156405</v>
+        <v>0.3369114835466984</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1618599461248437</v>
+        <v>0.1614237931356524</v>
       </c>
       <c r="R3" s="5">
         <v>55</v>
@@ -2336,16 +2336,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06679043190940723</v>
+        <v>0.007525623244632129</v>
       </c>
       <c r="O4" s="5">
         <v>55</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4703126602349408</v>
+        <v>0.4594150766580857</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2014198024595817</v>
+        <v>0.1980405799488641</v>
       </c>
       <c r="R4" s="5">
         <v>55</v>
@@ -2518,16 +2518,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07007191630118163</v>
+        <v>-0.07685580133788505</v>
       </c>
       <c r="O3" s="5">
         <v>58</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2622163815978738</v>
+        <v>0.2614815491555694</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1181767907808315</v>
+        <v>0.118042383350282</v>
       </c>
       <c r="R3" s="5">
         <v>58</v>
@@ -2577,16 +2577,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03860904106452706</v>
+        <v>-0.09615757615965492</v>
       </c>
       <c r="O4" s="5">
         <v>62</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3697092988382296</v>
+        <v>0.3537867842955421</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.175019201462059</v>
+        <v>0.1617822366324322</v>
       </c>
       <c r="R4" s="5">
         <v>62</v>
@@ -2759,16 +2759,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1943751549370077</v>
+        <v>-0.2058098045678776</v>
       </c>
       <c r="O3" s="5">
         <v>55</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3390607694297748</v>
+        <v>0.3383806658500514</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1241649952972282</v>
+        <v>0.1235567737221214</v>
       </c>
       <c r="R3" s="5">
         <v>55</v>
@@ -2818,16 +2818,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.007403649582524647</v>
+        <v>-0.04248258528073734</v>
       </c>
       <c r="O4" s="5">
         <v>59</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4081489282985624</v>
+        <v>0.4016105354582469</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1590972022596665</v>
+        <v>0.156010714918234</v>
       </c>
       <c r="R4" s="5">
         <v>59</v>
@@ -3000,16 +3000,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1687255319506957</v>
+        <v>0.2285304435907141</v>
       </c>
       <c r="O3" s="5">
         <v>49</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6017600223535065</v>
+        <v>0.5942791091983373</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1712870962346686</v>
+        <v>0.1575492390272969</v>
       </c>
       <c r="R3" s="5">
         <v>49</v>
@@ -3059,16 +3059,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3687717428578802</v>
+        <v>0.3981189301678976</v>
       </c>
       <c r="O4" s="5">
         <v>46</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9931098920157776</v>
+        <v>0.9985542355797584</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4380253587715026</v>
+        <v>0.4369050555732961</v>
       </c>
       <c r="R4" s="5">
         <v>46</v>
@@ -3241,16 +3241,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3809241676304118</v>
+        <v>-0.3950800480874967</v>
       </c>
       <c r="O3" s="5">
         <v>59</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2411495265234379</v>
+        <v>0.2393926899277877</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08389101066452909</v>
+        <v>0.08264552636043322</v>
       </c>
       <c r="R3" s="5">
         <v>59</v>
@@ -3300,16 +3300,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2302978855912419</v>
+        <v>-0.2705228723089732</v>
       </c>
       <c r="O4" s="5">
         <v>60</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3223200144524288</v>
+        <v>0.3164687032824758</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1381594921027779</v>
+        <v>0.1344047155970118</v>
       </c>
       <c r="R4" s="5">
         <v>60</v>
@@ -3482,16 +3482,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4929804585723163</v>
+        <v>0.5044505235219821</v>
       </c>
       <c r="O3" s="5">
         <v>43</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7530248439223374</v>
+        <v>0.7551103102768219</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1545855758960396</v>
+        <v>0.1543188301995358</v>
       </c>
       <c r="R3" s="5">
         <v>43</v>
@@ -3541,16 +3541,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4748502474099966</v>
+        <v>0.556643746621476</v>
       </c>
       <c r="O4" s="5">
         <v>33</v>
       </c>
       <c r="P4" s="4">
-        <v>1.416181157206347</v>
+        <v>1.437866936875494</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3998539785200312</v>
+        <v>0.3895768343740806</v>
       </c>
       <c r="R4" s="5">
         <v>31</v>
@@ -3723,16 +3723,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2468265761497209</v>
+        <v>-0.2513276324398532</v>
       </c>
       <c r="O3" s="5">
         <v>58</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1209790447674709</v>
+        <v>0.1205967918163422</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09645858212502074</v>
+        <v>0.09633402230409031</v>
       </c>
       <c r="R3" s="5">
         <v>58</v>
@@ -3782,16 +3782,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2166541696864906</v>
+        <v>-0.2270634422468447</v>
       </c>
       <c r="O4" s="5">
         <v>62</v>
       </c>
       <c r="P4" s="4">
-        <v>0.242755597886884</v>
+        <v>0.2412821926401501</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1405582498082352</v>
+        <v>0.139661352130122</v>
       </c>
       <c r="R4" s="5">
         <v>62</v>
@@ -3928,13 +3928,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4919295240089842</v>
+        <v>0.4861107428472746</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1912737337382286</v>
+        <v>0.1902464024122062</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1796131307095432</v>
+        <v>0.1809678616526462</v>
       </c>
       <c r="K3" s="4">
         <v>76.77205730777128</v>
@@ -3978,13 +3978,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3038364648992409</v>
+        <v>0.3023694179736083</v>
       </c>
       <c r="I4" s="4">
-        <v>0.2337041063181899</v>
+        <v>0.230954410281186</v>
       </c>
       <c r="J4" s="4">
-        <v>0.2067103207104186</v>
+        <v>0.2044221092772679</v>
       </c>
       <c r="K4" s="4">
         <v>79.71835703978549</v>
@@ -4028,13 +4028,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.344515116446364</v>
+        <v>0.3372440986101092</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1639516097690043</v>
+        <v>0.1592726347679443</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1675462629417466</v>
+        <v>0.166975510335764</v>
       </c>
       <c r="K5" s="4">
         <v>84.25298907441727</v>
@@ -4078,13 +4078,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3581693304450327</v>
+        <v>0.3472587020688322</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2012570439824828</v>
+        <v>0.1942378973412862</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1951679596474923</v>
+        <v>0.1892949005552805</v>
       </c>
       <c r="K6" s="4">
         <v>82.80638012780898</v>
@@ -4128,13 +4128,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.2470769747945377</v>
+        <v>0.2389882612443013</v>
       </c>
       <c r="I7" s="4">
-        <v>0.1072335361019085</v>
+        <v>0.1010293919059218</v>
       </c>
       <c r="J7" s="4">
-        <v>0.1059192629621992</v>
+        <v>0.1027289845888795</v>
       </c>
       <c r="K7" s="4">
         <v>87.32580911152297</v>
@@ -4178,13 +4178,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.3516773637345433</v>
+        <v>0.3488247609350674</v>
       </c>
       <c r="I8" s="4">
-        <v>0.202125871742114</v>
+        <v>0.1999670604378506</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1901962975521154</v>
+        <v>0.1919950635537022</v>
       </c>
       <c r="K8" s="4">
         <v>82.38584827870598</v>
@@ -4228,13 +4228,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.5177580314233875</v>
+        <v>0.515818769843532</v>
       </c>
       <c r="I9" s="4">
-        <v>0.2866858732403553</v>
+        <v>0.2854615253298631</v>
       </c>
       <c r="J9" s="4">
-        <v>0.2613537700138544</v>
+        <v>0.2608258327439179</v>
       </c>
       <c r="K9" s="4">
         <v>75.35070088641534</v>
@@ -4278,13 +4278,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.4500123753974742</v>
+        <v>0.450044986479941</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1433296714397258</v>
+        <v>0.1412213249527228</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1448631815301744</v>
+        <v>0.1442205998567737</v>
       </c>
       <c r="K10" s="4">
         <v>85.28937332508755</v>
@@ -4328,13 +4328,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.4049551323752907</v>
+        <v>0.398163280102392</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1816398742922127</v>
+        <v>0.1797321865422583</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1686967740216966</v>
+        <v>0.1674164913404225</v>
       </c>
       <c r="K11" s="4">
         <v>83.40136054421781</v>
@@ -4378,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.3159628402180517</v>
+        <v>0.3076341667255557</v>
       </c>
       <c r="I12" s="4">
-        <v>0.147545369632799</v>
+        <v>0.1406413075460596</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1445574559893458</v>
+        <v>0.1384535917202654</v>
       </c>
       <c r="K12" s="4">
         <v>88.65285508142607</v>
@@ -4428,13 +4428,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.3736048488641686</v>
+        <v>0.3699956006541491</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1422439445146305</v>
+        <v>0.1403531117095832</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1415332351804637</v>
+        <v>0.1409093252863823</v>
       </c>
       <c r="K13" s="4">
         <v>83.2588641517213</v>
@@ -4478,13 +4478,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.797434957184642</v>
+        <v>0.7964166723890479</v>
       </c>
       <c r="I14" s="4">
-        <v>0.3004445707261883</v>
+        <v>0.2928162659864123</v>
       </c>
       <c r="J14" s="4">
-        <v>0.3382397932373646</v>
+        <v>0.3244076306076369</v>
       </c>
       <c r="K14" s="4">
         <v>69.16177076891383</v>
@@ -4528,13 +4528,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2817347704879333</v>
+        <v>0.2779306966051318</v>
       </c>
       <c r="I15" s="4">
-        <v>0.111253270213226</v>
+        <v>0.1087425965637501</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1162190895256763</v>
+        <v>0.1149269376620512</v>
       </c>
       <c r="K15" s="4">
         <v>89.68176664605306</v>
@@ -4578,13 +4578,13 @@
         <v>1.515151515151515</v>
       </c>
       <c r="H16" s="4">
-        <v>1.084603000564342</v>
+        <v>1.096488623576158</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2573331499682523</v>
+        <v>0.2528728589753585</v>
       </c>
       <c r="J16" s="4">
-        <v>0.3806028066734234</v>
+        <v>0.3719898913832622</v>
       </c>
       <c r="K16" s="4">
         <v>60.15744176458471</v>
@@ -4628,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1818673213271775</v>
+        <v>0.1809394922282462</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1192434104280149</v>
+        <v>0.1187198093808733</v>
       </c>
       <c r="J17" s="4">
-        <v>0.1197832618543381</v>
+        <v>0.1194803672994585</v>
       </c>
       <c r="K17" s="4">
         <v>88.97366522366443</v>
@@ -6331,16 +6331,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.03138994436115752</v>
+        <v>0.02543214647155878</v>
       </c>
       <c r="O3" s="5">
         <v>45</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5025936302794297</v>
+        <v>0.501149315639527</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1709127754609125</v>
+        <v>0.1707803799522547</v>
       </c>
       <c r="R3" s="5">
         <v>45</v>
@@ -6390,16 +6390,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1472792623903235</v>
+        <v>0.09919540041320118</v>
       </c>
       <c r="O4" s="5">
         <v>54</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4812654177385385</v>
+        <v>0.4710721700550221</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2082411989693254</v>
+        <v>0.2064680877954991</v>
       </c>
       <c r="R4" s="5">
         <v>54</v>
@@ -6572,16 +6572,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01431298042295354</v>
+        <v>0.02560024419738482</v>
       </c>
       <c r="O3" s="5">
         <v>52</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3517540098074124</v>
+        <v>0.3532444974820121</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2532767995308038</v>
+        <v>0.2529979446996359</v>
       </c>
       <c r="R3" s="5">
         <v>52</v>
@@ -6631,16 +6631,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1623651931226708</v>
+        <v>0.1073952366601532</v>
       </c>
       <c r="O4" s="5">
         <v>57</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2559189199910694</v>
+        <v>0.2514943384652045</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2158483160189631</v>
+        <v>0.2108445192327755</v>
       </c>
       <c r="R4" s="5">
         <v>57</v>
@@ -6813,16 +6813,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.06706215144961752</v>
+        <v>-0.08824553028759397</v>
       </c>
       <c r="O3" s="5">
         <v>57</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2002758117418247</v>
+        <v>0.1989919706001291</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1365239505810064</v>
+        <v>0.1361523123557787</v>
       </c>
       <c r="R3" s="5">
         <v>57</v>
@@ -6872,16 +6872,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.01709720897037778</v>
+        <v>-0.09235211655797571</v>
       </c>
       <c r="O4" s="5">
         <v>59</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4887544211509035</v>
+        <v>0.4754962266200892</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1904495177980869</v>
+        <v>0.1816092174373246</v>
       </c>
       <c r="R4" s="5">
         <v>59</v>
@@ -7054,16 +7054,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.02391658558893968</v>
+        <v>-0.07585108042053434</v>
       </c>
       <c r="O3" s="5">
         <v>53</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4836228306573483</v>
+        <v>0.4725076443346051</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1834531198450985</v>
+        <v>0.1786388166395193</v>
       </c>
       <c r="R3" s="5">
         <v>53</v>
@@ -7113,16 +7113,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.01367851440703795</v>
+        <v>-0.05917054917357945</v>
       </c>
       <c r="O4" s="5">
         <v>58</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2327158302327172</v>
+        <v>0.2220097598030592</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2175261470735408</v>
+        <v>0.2084922297066939</v>
       </c>
       <c r="R4" s="5">
         <v>58</v>
@@ -7295,16 +7295,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01485967995674807</v>
+        <v>-0.02426253339721995</v>
       </c>
       <c r="O3" s="5">
         <v>56</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1097374242338208</v>
+        <v>0.1081751436625522</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0727362076703115</v>
+        <v>0.07156658081420719</v>
       </c>
       <c r="R3" s="5">
         <v>56</v>
@@ -7354,16 +7354,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.02970104342816024</v>
+        <v>-0.01212604363037428</v>
       </c>
       <c r="O4" s="5">
         <v>58</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3844165253552547</v>
+        <v>0.3698013788260505</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.14054130148414</v>
+        <v>0.1294762439944738</v>
       </c>
       <c r="R4" s="5">
         <v>58</v>
